--- a/data/stx_xlsx/KDV.ST.xlsx
+++ b/data/stx_xlsx/KDV.ST.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="309">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -583,6 +583,12 @@
   </si>
   <si>
     <t>Deferred Taxes</t>
+  </si>
+  <si>
+    <t>Convertible loan (Do not use)</t>
+  </si>
+  <si>
+    <t>Other financial liabilities (Do not use)</t>
   </si>
   <si>
     <t>Total Long-term liabilities</t>
@@ -1065,7 +1071,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1146,6 +1152,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -8940,8 +8949,8 @@
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="14" t="s">
-        <v>184</v>
+      <c r="A71" s="27" t="s">
+        <v>188</v>
       </c>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
@@ -8977,8 +8986,8 @@
       <c r="S71" s="21"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="14" t="s">
-        <v>175</v>
+      <c r="A72" s="27" t="s">
+        <v>189</v>
       </c>
       <c r="B72" s="21"/>
       <c r="C72" s="21"/>
@@ -9017,7 +9026,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B73" s="26"/>
       <c r="C73" s="26"/>
@@ -9064,7 +9073,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B74" s="17">
         <v>9.12</v>
@@ -9123,7 +9132,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B75" s="15">
         <v>2.95</v>
@@ -9182,7 +9191,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B76" s="18">
         <v>2991.62</v>
@@ -9241,7 +9250,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B77" s="20">
         <v>-1852.04</v>
@@ -9300,7 +9309,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B78" s="21"/>
       <c r="C78" s="21"/>
@@ -9325,7 +9334,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="16" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B79" s="22">
         <v>1142.53</v>
@@ -9384,7 +9393,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B80" s="21"/>
       <c r="C80" s="21"/>
@@ -9415,7 +9424,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B81" s="26"/>
       <c r="C81" s="26"/>
@@ -9446,7 +9455,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="16" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B82" s="22">
         <v>1142.53</v>
@@ -9505,7 +9514,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B83" s="22">
         <v>1151.65</v>
@@ -9564,7 +9573,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B84" s="18">
         <v>331.73</v>
@@ -9623,7 +9632,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B85" s="18">
         <v>331.73</v>
@@ -9682,7 +9691,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B86" s="21">
         <v>0.0</v>
@@ -9741,7 +9750,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B87" s="21"/>
       <c r="C87" s="21"/>
@@ -9770,7 +9779,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B88" s="21"/>
       <c r="C88" s="21"/>
@@ -9799,7 +9808,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B89" s="21"/>
       <c r="C89" s="21"/>
@@ -9830,7 +9839,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B90" s="21"/>
       <c r="C90" s="15">
@@ -9863,7 +9872,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B91" s="15">
         <v>2.56</v>
@@ -9922,7 +9931,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B92" s="15">
         <v>2.56</v>
@@ -9981,7 +9990,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B93" s="15">
         <v>0.01</v>
@@ -10034,7 +10043,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B94" s="15">
         <v>0.99</v>
@@ -10093,7 +10102,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B95" s="21">
         <v>0.0</v>
@@ -10152,7 +10161,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B96" s="18">
         <v>328.59</v>
@@ -10211,7 +10220,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B97" s="18">
         <v>328.59</v>
@@ -11193,7 +11202,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11527,58 +11536,58 @@
         <v>40</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -11642,7 +11651,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -11838,7 +11847,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B22" s="18">
         <v>190.01</v>
@@ -11897,7 +11906,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B23" s="21"/>
       <c r="C23" s="19">
@@ -11948,7 +11957,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B24" s="19">
         <v>-6.52</v>
@@ -11973,7 +11982,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B25" s="15">
         <v>0.36</v>
@@ -11998,7 +12007,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -12043,7 +12052,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -12088,7 +12097,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -12119,7 +12128,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -12156,7 +12165,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B30" s="19">
         <v>-20.71</v>
@@ -12205,7 +12214,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B31" s="19">
         <v>-2.83</v>
@@ -12264,7 +12273,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B32" s="19">
         <v>-4.07</v>
@@ -12323,7 +12332,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -12354,7 +12363,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -12383,7 +12392,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -12410,7 +12419,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -12441,7 +12450,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B37" s="21"/>
       <c r="C37" s="21"/>
@@ -12472,7 +12481,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B38" s="21"/>
       <c r="C38" s="21"/>
@@ -12503,7 +12512,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="16" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B39" s="24">
         <v>-27.6</v>
@@ -12562,7 +12571,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -12595,7 +12604,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
@@ -12628,7 +12637,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B42" s="15">
         <v>0.51</v>
@@ -12669,7 +12678,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B43" s="15">
         <v>68.01</v>
@@ -12696,7 +12705,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
@@ -12729,7 +12738,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B45" s="19">
         <v>-58.96</v>
@@ -12770,7 +12779,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
@@ -12805,7 +12814,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -12832,7 +12841,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B48" s="21"/>
       <c r="C48" s="21">
@@ -12867,7 +12876,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
@@ -12900,7 +12909,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -12933,7 +12942,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
@@ -12962,7 +12971,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
@@ -12995,7 +13004,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
@@ -13028,7 +13037,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -13061,7 +13070,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
@@ -13088,7 +13097,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
@@ -13121,7 +13130,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="16" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B57" s="17">
         <v>9.56</v>
@@ -13172,7 +13181,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
@@ -13201,7 +13210,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
@@ -13246,7 +13255,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
@@ -13275,7 +13284,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -13322,7 +13331,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
@@ -13353,7 +13362,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
@@ -13380,7 +13389,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
@@ -13409,7 +13418,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
@@ -13436,7 +13445,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B66" s="19">
         <v>-1.13</v>
@@ -13471,7 +13480,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B67" s="24">
         <v>-1.13</v>
@@ -13530,7 +13539,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
@@ -13555,7 +13564,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="16" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B69" s="26"/>
       <c r="C69" s="26"/>
@@ -13580,7 +13589,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B70" s="15">
         <v>45.94</v>
@@ -13639,7 +13648,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B71" s="15">
         <v>26.15</v>
@@ -13698,7 +13707,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="16" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B72" s="24">
         <v>-19.17</v>
@@ -14705,7 +14714,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14855,10 +14864,10 @@
         <v>35</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -15173,7 +15182,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -15251,1427 +15260,1427 @@
         <v>62</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T19" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
+      <c r="A20" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="31">
         <v>212.2</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>368.48</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>293.02</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>941.7</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>287.59</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>558.31</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>721.22</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>579.01</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="31">
         <v>441.96</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>576.3</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>545.35</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>1180.44</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>373.82</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>698.61</v>
       </c>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="31"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="31"/>
-      <c r="T21" s="31"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="B22" s="31">
         <v>437.08</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>506.34</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>543.63</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>614.79</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <v>554.39</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <v>549.44</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <v>566.66</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>683.81</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>621.12</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>756.45</v>
       </c>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="31"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="31"/>
-      <c r="T22" s="31"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
+      <c r="A23" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>270</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="B24" s="31">
         <v>264.62</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>461.69</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>486.01</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>909.61</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>329.85</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>580.87</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>389.97</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>369.33</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="31">
         <v>303.23</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>521.91</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>658.9</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>1369.55</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>615.94</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>979.36</v>
       </c>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="B25" s="31">
         <v>510.31</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>572.63</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>524.28</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>513.97</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>422.66</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>413.82</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>443.93</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>666.06</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>697.69</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>939.29</v>
       </c>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
+      <c r="A26" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="B27" s="33">
         <v>0.98</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>1.71</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>1.63</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32">
+      <c r="E27" s="32"/>
+      <c r="F27" s="33">
         <v>1.66</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>2.93</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>5.38</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>5.1</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>5.04</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>8.9</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>11.25</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <v>25.79</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <v>11.6</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>18.44</v>
       </c>
-      <c r="P27" s="31"/>
-      <c r="Q27" s="31"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>274</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" s="33">
         <v>2.2</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>2.59</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>3.14</v>
       </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32">
+      <c r="E28" s="32"/>
+      <c r="F28" s="33">
         <v>4.31</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>5.16</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>7.06</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>11.61</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="33">
         <v>12.6</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="33">
         <v>17.25</v>
       </c>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
+      <c r="A29" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B30" s="34">
         <v>-8.81</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>-4.45</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>-5.95</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="35">
         <v>1.46</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>-10.51</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>-2.84</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>3.3</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>-8.85</v>
       </c>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="33">
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="34">
         <v>-21.53</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>-12.93</v>
       </c>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="34"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" s="34">
         <v>-3.38</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>-2.85</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>-0.65</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>-2.28</v>
       </c>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
+      <c r="A32" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" s="33">
         <v>0.25</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>0.45</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="33">
         <v>0.46</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="33">
         <v>1.18</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="33">
         <v>0.4</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <v>0.62</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <v>1.35</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="33">
         <v>1.38</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="33">
         <v>10.71</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="33">
         <v>2.06</v>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="33">
         <v>0.56</v>
       </c>
-      <c r="M33" s="32">
+      <c r="M33" s="33">
         <v>0.76</v>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="33">
         <v>0.35</v>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="33">
         <v>0.62</v>
       </c>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
-      <c r="T33" s="31"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="B34" s="33">
         <v>0.58</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>0.68</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>0.9</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="33">
         <v>1.13</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="33">
         <v>1.19</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <v>1.58</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="33">
         <v>1.08</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="33">
         <v>0.89</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="33">
         <v>0.66</v>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="33">
         <v>0.62</v>
       </c>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="31"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
+      <c r="A35" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B36" s="33">
         <v>0.25</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>0.45</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>0.46</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="33">
         <v>1.18</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="33">
         <v>0.4</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <v>0.62</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="33">
         <v>1.35</v>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="33">
         <v>1.38</v>
       </c>
-      <c r="J36" s="32">
+      <c r="J36" s="33">
         <v>10.71</v>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="33">
         <v>2.06</v>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="33">
         <v>0.56</v>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="33">
         <v>0.76</v>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="33">
         <v>0.35</v>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="33">
         <v>0.99</v>
       </c>
-      <c r="P36" s="31"/>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
-      <c r="S36" s="31"/>
-      <c r="T36" s="31"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B37" s="32">
+      <c r="A37" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B37" s="33">
         <v>0.55</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="33">
         <v>0.62</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="33">
         <v>0.8</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E37" s="33">
         <v>0.96</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="33">
         <v>1.19</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="33">
         <v>1.58</v>
       </c>
-      <c r="H37" s="32">
+      <c r="H37" s="33">
         <v>1.08</v>
       </c>
-      <c r="I37" s="32">
+      <c r="I37" s="33">
         <v>0.89</v>
       </c>
-      <c r="J37" s="32">
+      <c r="J37" s="33">
         <v>0.66</v>
       </c>
-      <c r="K37" s="32">
+      <c r="K37" s="33">
         <v>0.68</v>
       </c>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
+      <c r="A38" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B39" s="30">
+      <c r="A39" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="B39" s="31">
         <v>171.84</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <v>279.42</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <v>237.82</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <v>528.23</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <v>119.11</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>77.06</v>
       </c>
-      <c r="H39" s="30">
+      <c r="H39" s="31">
         <v>129.82</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="31">
         <v>143.05</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>59.56</v>
       </c>
-      <c r="K39" s="30">
+      <c r="K39" s="31">
         <v>173.44</v>
       </c>
-      <c r="L39" s="30">
+      <c r="L39" s="31">
         <v>128.04</v>
       </c>
-      <c r="M39" s="30">
+      <c r="M39" s="31">
         <v>301.94</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>74.68</v>
       </c>
-      <c r="O39" s="30">
+      <c r="O39" s="31">
         <v>100.56</v>
       </c>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="B40" s="30">
+      <c r="A40" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="B40" s="31">
         <v>259.38</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="31">
         <v>168.72</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="31">
         <v>148.08</v>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="31">
         <v>142.17</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="33">
         <v>93.29</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="31">
         <v>107.24</v>
       </c>
-      <c r="H40" s="30">
+      <c r="H40" s="31">
         <v>117.41</v>
       </c>
-      <c r="I40" s="30">
+      <c r="I40" s="31">
         <v>162.89</v>
       </c>
-      <c r="J40" s="30">
+      <c r="J40" s="31">
         <v>132.41</v>
       </c>
-      <c r="K40" s="30">
+      <c r="K40" s="31">
         <v>132.04</v>
       </c>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
+      <c r="A41" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="32">
+      <c r="A42" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="33">
         <v>68.63</v>
       </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="32">
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="33">
         <v>30.33</v>
       </c>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
+      <c r="A43" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32">
+      <c r="A44" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B44" s="32"/>
+      <c r="C44" s="33">
         <v>91.0</v>
       </c>
-      <c r="D44" s="31"/>
-      <c r="E44" s="32">
+      <c r="D44" s="32"/>
+      <c r="E44" s="33">
         <v>6.68</v>
       </c>
-      <c r="F44" s="31"/>
-      <c r="G44" s="32">
+      <c r="F44" s="32"/>
+      <c r="G44" s="33">
         <v>0.86</v>
       </c>
-      <c r="H44" s="31"/>
-      <c r="I44" s="32">
+      <c r="H44" s="32"/>
+      <c r="I44" s="33">
         <v>1.96</v>
       </c>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="31"/>
-      <c r="N44" s="31"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="31"/>
-      <c r="Q44" s="31"/>
-      <c r="R44" s="31"/>
-      <c r="S44" s="31"/>
-      <c r="T44" s="31"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
+      <c r="M44" s="32"/>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32"/>
+      <c r="T44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="32">
+      <c r="A45" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="B45" s="32"/>
+      <c r="C45" s="33">
         <v>4.23</v>
       </c>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="31"/>
-      <c r="N45" s="31"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="31"/>
-      <c r="Q45" s="31"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="31"/>
-      <c r="T45" s="31"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
+      <c r="O45" s="32"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="32"/>
+      <c r="R45" s="32"/>
+      <c r="S45" s="32"/>
+      <c r="T45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
+      <c r="A46" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="30">
+      <c r="A47" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="31">
         <v>104.49</v>
       </c>
-      <c r="D47" s="31"/>
-      <c r="E47" s="32">
+      <c r="D47" s="32"/>
+      <c r="E47" s="33">
         <v>6.71</v>
       </c>
-      <c r="F47" s="31"/>
-      <c r="G47" s="32">
+      <c r="F47" s="32"/>
+      <c r="G47" s="33">
         <v>0.86</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="33">
         <v>13.08</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="33">
         <v>1.96</v>
       </c>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="31"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="32">
+      <c r="A48" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="B48" s="32"/>
+      <c r="C48" s="33">
         <v>4.25</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>4.86</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <v>3.18</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="33">
         <v>10.36</v>
       </c>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="31"/>
-      <c r="N48" s="31"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="31"/>
-      <c r="Q48" s="31"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="31"/>
-      <c r="T48" s="31"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="32"/>
+      <c r="M48" s="32"/>
+      <c r="N48" s="32"/>
+      <c r="O48" s="32"/>
+      <c r="P48" s="32"/>
+      <c r="Q48" s="32"/>
+      <c r="R48" s="32"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
+      <c r="A49" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" s="33">
         <v>0.55</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>0.62</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>0.8</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>0.96</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <v>1.19</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>1.58</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <v>1.08</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="33">
         <v>0.89</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="33">
         <v>0.66</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>0.62</v>
       </c>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="32"/>
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="28"/>
-      <c r="S51" s="28"/>
-      <c r="T51" s="28"/>
+      <c r="A51" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="29"/>
+      <c r="S51" s="29"/>
+      <c r="T51" s="29"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="32">
+      <c r="A52" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="33">
         <v>0.99</v>
       </c>
-      <c r="D52" s="31"/>
-      <c r="E52" s="32">
+      <c r="D52" s="32"/>
+      <c r="E52" s="33">
         <v>0.04</v>
       </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31">
+      <c r="F52" s="32"/>
+      <c r="G52" s="32">
         <v>0.0</v>
       </c>
-      <c r="H52" s="35">
+      <c r="H52" s="36">
         <v>-0.16</v>
       </c>
-      <c r="I52" s="32">
+      <c r="I52" s="33">
         <v>0.01</v>
       </c>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
-      <c r="N52" s="31"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="31"/>
-      <c r="S52" s="31"/>
-      <c r="T52" s="31"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="35">
+      <c r="A53" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" s="32"/>
+      <c r="C53" s="36">
         <v>-0.09</v>
       </c>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="32"/>
+      <c r="M53" s="32"/>
+      <c r="N53" s="32"/>
+      <c r="O53" s="32"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="32"/>
+      <c r="R53" s="32"/>
+      <c r="S53" s="32"/>
+      <c r="T53" s="32"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="28"/>
-      <c r="R54" s="28"/>
-      <c r="S54" s="28"/>
-      <c r="T54" s="28"/>
+      <c r="A54" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="29"/>
+      <c r="S54" s="29"/>
+      <c r="T54" s="29"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="B55" s="30">
+      <c r="A55" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B55" s="31">
         <v>112.3</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="31">
         <v>181.73</v>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="31">
         <v>135.35</v>
       </c>
-      <c r="E55" s="30">
+      <c r="E55" s="31">
         <v>445.42</v>
       </c>
-      <c r="F55" s="30">
+      <c r="F55" s="31">
         <v>103.89</v>
       </c>
-      <c r="G55" s="30">
+      <c r="G55" s="31">
         <v>175.95</v>
       </c>
-      <c r="H55" s="30">
+      <c r="H55" s="31">
         <v>240.5</v>
       </c>
-      <c r="I55" s="30">
+      <c r="I55" s="31">
         <v>234.84</v>
       </c>
-      <c r="J55" s="32">
+      <c r="J55" s="33">
         <v>86.95</v>
       </c>
-      <c r="K55" s="30">
+      <c r="K55" s="31">
         <v>187.17</v>
       </c>
-      <c r="L55" s="30">
+      <c r="L55" s="31">
         <v>113.11</v>
       </c>
-      <c r="M55" s="30">
+      <c r="M55" s="31">
         <v>253.14</v>
       </c>
-      <c r="N55" s="32">
+      <c r="N55" s="33">
         <v>43.92</v>
       </c>
-      <c r="O55" s="32">
+      <c r="O55" s="33">
         <v>76.83</v>
       </c>
-      <c r="P55" s="31"/>
-      <c r="Q55" s="31"/>
-      <c r="R55" s="31"/>
-      <c r="S55" s="31"/>
-      <c r="T55" s="31"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="B56" s="30">
+      <c r="A56" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="B56" s="31">
         <v>193.72</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C56" s="31">
         <v>200.87</v>
       </c>
-      <c r="D56" s="30">
+      <c r="D56" s="31">
         <v>212.68</v>
       </c>
-      <c r="E56" s="30">
+      <c r="E56" s="31">
         <v>229.6</v>
       </c>
-      <c r="F56" s="30">
+      <c r="F56" s="31">
         <v>156.78</v>
       </c>
-      <c r="G56" s="30">
+      <c r="G56" s="31">
         <v>170.11</v>
       </c>
-      <c r="H56" s="30">
+      <c r="H56" s="31">
         <v>153.87</v>
       </c>
-      <c r="I56" s="30">
+      <c r="I56" s="31">
         <v>164.71</v>
       </c>
-      <c r="J56" s="30">
+      <c r="J56" s="31">
         <v>116.04</v>
       </c>
-      <c r="K56" s="30">
+      <c r="K56" s="31">
         <v>108.39</v>
       </c>
-      <c r="L56" s="31"/>
-      <c r="M56" s="31"/>
-      <c r="N56" s="31"/>
-      <c r="O56" s="31"/>
-      <c r="P56" s="31"/>
-      <c r="Q56" s="31"/>
-      <c r="R56" s="31"/>
-      <c r="S56" s="31"/>
-      <c r="T56" s="31"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="32"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="32"/>
+      <c r="T56" s="32"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
-      <c r="Q57" s="28"/>
-      <c r="R57" s="28"/>
-      <c r="S57" s="28"/>
-      <c r="T57" s="28"/>
+      <c r="A57" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="32">
+      <c r="A58" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="33">
         <v>57.87</v>
       </c>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="32">
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="33">
         <v>56.19</v>
       </c>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
-      <c r="M59" s="28"/>
-      <c r="N59" s="28"/>
-      <c r="O59" s="28"/>
-      <c r="P59" s="28"/>
-      <c r="Q59" s="28"/>
-      <c r="R59" s="28"/>
-      <c r="S59" s="28"/>
-      <c r="T59" s="28"/>
+      <c r="A59" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="29"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="29"/>
+      <c r="P59" s="29"/>
+      <c r="Q59" s="29"/>
+      <c r="R59" s="29"/>
+      <c r="S59" s="29"/>
+      <c r="T59" s="29"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
-        <v>306</v>
-      </c>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="32">
+      <c r="A60" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="33">
         <v>57.87</v>
       </c>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="32">
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="33">
         <v>56.19</v>
       </c>
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
-      <c r="N60" s="31"/>
-      <c r="O60" s="31"/>
-      <c r="P60" s="31"/>
-      <c r="Q60" s="31"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="31"/>
-      <c r="T60" s="31"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32"/>
+      <c r="N60" s="32"/>
+      <c r="O60" s="32"/>
+      <c r="P60" s="32"/>
+      <c r="Q60" s="32"/>
+      <c r="R60" s="32"/>
+      <c r="S60" s="32"/>
+      <c r="T60" s="32"/>
     </row>
     <row r="61" ht="15.75" customHeight="1"/>
     <row r="62" ht="15.75" customHeight="1"/>
